--- a/results/DR_results/01_pollution_assessment/HZD_Toxicity/artifacts/HZD_01_updated_data.xlsx
+++ b/results/DR_results/01_pollution_assessment/HZD_Toxicity/artifacts/HZD_01_updated_data.xlsx
@@ -506,11 +506,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>546.8862872709975</v>
+        <v>100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -521,11 +521,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>360.6353167654386</v>
+        <v>100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -536,11 +536,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>323.051407701296</v>
+        <v>100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -551,11 +551,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2556.139459613995</v>
+        <v>100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -566,11 +566,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>389.1447595169337</v>
+        <v>100</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -581,11 +581,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>323.0207538464629</v>
+        <v>100</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -596,11 +596,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>965.0597246895593</v>
+        <v>100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -611,11 +611,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>626.3454772460516</v>
+        <v>100</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -626,11 +626,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>555.7541358872287</v>
+        <v>100</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -641,11 +641,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>596.2944182421847</v>
+        <v>100</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -656,11 +656,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>455.2901281447499</v>
+        <v>100</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>367.9311051558853</v>
+        <v>100</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -686,11 +686,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>245.1926159538724</v>
+        <v>100</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -701,11 +701,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>856.6217823212094</v>
+        <v>100</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3855.607461612087</v>
+        <v>100</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -731,11 +731,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1149.724994108823</v>
+        <v>100</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -746,11 +746,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>207.0579438659458</v>
+        <v>100</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -761,11 +761,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2039.584531727344</v>
+        <v>100</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -776,11 +776,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>337.3607090928327</v>
+        <v>100</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -791,11 +791,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1280.055962132029</v>
+        <v>100</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -806,11 +806,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1336.455020765899</v>
+        <v>100</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -821,11 +821,11 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1260.930648651318</v>
+        <v>100</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -836,11 +836,11 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>724.5505919915011</v>
+        <v>100</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -851,11 +851,11 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>498.4759345244664</v>
+        <v>100</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -866,11 +866,11 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>294.0369370837824</v>
+        <v>100</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -881,11 +881,11 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>291.8593637161068</v>
+        <v>100</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -896,11 +896,11 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>620.0084421057505</v>
+        <v>100</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -911,11 +911,11 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>370.5239447808135</v>
+        <v>100</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -926,11 +926,11 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>360.7196949436424</v>
+        <v>100</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -941,11 +941,11 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1547.418445218523</v>
+        <v>100</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -956,11 +956,11 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2444.610007996022</v>
+        <v>100</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -971,11 +971,11 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>406.5795781388446</v>
+        <v>100</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -986,11 +986,11 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2022.805759516662</v>
+        <v>100</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1001,11 +1001,11 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>631.9144309478047</v>
+        <v>100</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1016,11 +1016,11 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2844.226360015358</v>
+        <v>100</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1031,11 +1031,11 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1032.145332995505</v>
+        <v>100</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1046,11 +1046,11 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>234.7532068771725</v>
+        <v>100</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1061,11 +1061,11 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>328.1116646398809</v>
+        <v>100</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1076,11 +1076,11 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2039.298832631272</v>
+        <v>100</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1091,11 +1091,11 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2936.464886550528</v>
+        <v>100</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1106,11 +1106,11 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>404.8127038009187</v>
+        <v>100</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1121,11 +1121,11 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1434.537304015319</v>
+        <v>100</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1136,11 +1136,11 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>480.5934958009264</v>
+        <v>100</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1151,11 +1151,11 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1595.603088504419</v>
+        <v>100</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>327.0548948471127</v>
+        <v>100</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1181,11 +1181,11 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2567.921701705455</v>
+        <v>100</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1196,11 +1196,11 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2925.875750432383</v>
+        <v>100</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2686.191880139867</v>
+        <v>100</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1226,11 +1226,11 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2524.560294320388</v>
+        <v>100</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1241,11 +1241,11 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>683.8857100183628</v>
+        <v>100</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1256,11 +1256,11 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3220.618650230261</v>
+        <v>100</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1271,11 +1271,11 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2321.289901301369</v>
+        <v>100</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1286,11 +1286,11 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>396.6112299329343</v>
+        <v>100</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1301,11 +1301,11 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1041.460472141753</v>
+        <v>100</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1316,11 +1316,11 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>259.7106245630908</v>
+        <v>100</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1331,11 +1331,11 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3618.987219158857</v>
+        <v>100</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1346,11 +1346,11 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>95.30282091625358</v>
+        <v>100</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1361,11 +1361,11 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1868.516971161154</v>
+        <v>100</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1376,11 +1376,11 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>360.3018697066473</v>
+        <v>100</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1391,11 +1391,11 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1131.118265712656</v>
+        <v>100</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1406,11 +1406,11 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>757.2518796502143</v>
+        <v>100</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1421,11 +1421,11 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>396.6243555823813</v>
+        <v>100</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1436,11 +1436,11 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2427.207442015336</v>
+        <v>100</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1451,11 +1451,11 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1207.542886770313</v>
+        <v>100</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1466,11 +1466,11 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>474.3285163878188</v>
+        <v>100</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1481,11 +1481,11 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2024.762538137933</v>
+        <v>100</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1496,11 +1496,11 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>955.5179229718462</v>
+        <v>100</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1511,11 +1511,11 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>771.5957150011114</v>
+        <v>100</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1526,11 +1526,11 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>3219.427834099502</v>
+        <v>100</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1541,11 +1541,11 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2862.402128390998</v>
+        <v>100</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1334.429688323259</v>
+        <v>100</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1571,11 +1571,11 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2015.888612882292</v>
+        <v>100</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1586,11 +1586,11 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1033.684920906245</v>
+        <v>100</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1601,11 +1601,11 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1256.055857684058</v>
+        <v>100</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1616,11 +1616,11 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>533.1034047186363</v>
+        <v>100</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1631,11 +1631,11 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>454.5250660126463</v>
+        <v>100</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1646,11 +1646,11 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2311.968018222636</v>
+        <v>100</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1661,11 +1661,11 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2808.049236778268</v>
+        <v>100</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1676,11 +1676,11 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1685.684089901667</v>
+        <v>100</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1691,11 +1691,11 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1180.338209126076</v>
+        <v>100</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1706,11 +1706,11 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1122.274824173758</v>
+        <v>100</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1721,11 +1721,11 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1659.615220500805</v>
+        <v>100</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1736,11 +1736,11 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>496.5426573352681</v>
+        <v>100</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1751,11 +1751,11 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>515.3802232348582</v>
+        <v>100</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1766,11 +1766,11 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>535.0407758200341</v>
+        <v>100</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1781,11 +1781,11 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2218.983006704507</v>
+        <v>100</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1796,11 +1796,11 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1413.758615588961</v>
+        <v>100</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1811,11 +1811,11 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>2489.46694485589</v>
+        <v>100</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1826,11 +1826,11 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>3824.762156001866</v>
+        <v>100</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1841,11 +1841,11 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>363.8787590418078</v>
+        <v>100</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1856,11 +1856,11 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>891.0246999633022</v>
+        <v>100</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1871,11 +1871,11 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>370.47640217286</v>
+        <v>100</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1886,11 +1886,11 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>441.6795858714871</v>
+        <v>100</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1901,11 +1901,11 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>987.6297528963544</v>
+        <v>100</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1916,11 +1916,11 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>283.2726392272232</v>
+        <v>100</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1931,11 +1931,11 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>381.4001161546993</v>
+        <v>100</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1946,11 +1946,11 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>373.1704849866163</v>
+        <v>100</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1961,11 +1961,11 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>875.5709275513107</v>
+        <v>100</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1976,11 +1976,11 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1358.858232890638</v>
+        <v>100</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1991,11 +1991,11 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>181.1997641153565</v>
+        <v>100</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2006,11 +2006,11 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>3179.781182840011</v>
+        <v>100</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2021,11 +2021,11 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>3142.640102524054</v>
+        <v>100</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2036,11 +2036,11 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>441.136470741838</v>
+        <v>100</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2051,11 +2051,11 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1039.188751641183</v>
+        <v>100</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2066,11 +2066,11 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>963.859908813514</v>
+        <v>100</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2081,11 +2081,11 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>910.127316173354</v>
+        <v>100</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2096,11 +2096,11 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>428.0664505928089</v>
+        <v>100</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2111,11 +2111,11 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>2694.184434639124</v>
+        <v>100</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2126,11 +2126,11 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>2003.593883557836</v>
+        <v>100</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2141,11 +2141,11 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>169.9943731212041</v>
+        <v>100</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2156,11 +2156,11 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>515.9467661722379</v>
+        <v>100</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2171,11 +2171,11 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>250.7853030719525</v>
+        <v>100</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2186,11 +2186,11 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>583.505704203978</v>
+        <v>100</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2201,11 +2201,11 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>311.7563898753855</v>
+        <v>100</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2216,11 +2216,11 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>198.2376242625456</v>
+        <v>100</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2231,11 +2231,11 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>513.1136162930709</v>
+        <v>100</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2246,11 +2246,11 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>336.9837854810057</v>
+        <v>100</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2261,11 +2261,11 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>496.7402313037054</v>
+        <v>100</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2276,11 +2276,11 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>336.3256766938426</v>
+        <v>100</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2291,11 +2291,11 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>793.5918378849225</v>
+        <v>100</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2306,11 +2306,11 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>255.8564348346725</v>
+        <v>100</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2321,11 +2321,11 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>343.7205495724889</v>
+        <v>100</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2336,11 +2336,11 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>296.5898617084659</v>
+        <v>100</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2351,11 +2351,11 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>401.0753779079404</v>
+        <v>100</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2366,11 +2366,11 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>2031.289738977498</v>
+        <v>100</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2381,11 +2381,11 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>351.1248217609392</v>
+        <v>100</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2396,11 +2396,11 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1095.356525225187</v>
+        <v>100</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2411,11 +2411,11 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>394.6835944254109</v>
+        <v>100</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2426,11 +2426,11 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5205546767190856</v>
+        <v>0</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2441,11 +2441,11 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.2270161697541991</v>
+        <v>0</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2456,11 +2456,11 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.1825130642224894</v>
+        <v>0</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2471,11 +2471,11 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.1130597803117607</v>
+        <v>0</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2486,11 +2486,11 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.1834459944775769</v>
+        <v>0</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2501,11 +2501,11 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.7470427322152114</v>
+        <v>34.23421327856809</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -2516,11 +2516,11 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.7295156377576173</v>
+        <v>24.58928343490263</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -2531,11 +2531,11 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>5.384312685924876</v>
+        <v>100</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2546,11 +2546,11 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5130559324059444</v>
+        <v>5.327838802008446</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -2561,11 +2561,11 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>1.084657664641707</v>
+        <v>40.97335249778372</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -2576,11 +2576,11 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>2.427564381354639</v>
+        <v>100</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2591,11 +2591,11 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.559125160484891</v>
+        <v>20.99222465691347</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -2606,11 +2606,11 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.7207287762010216</v>
+        <v>22.25386589281224</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -2621,11 +2621,11 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.3900247357395382</v>
+        <v>5.091373116196439</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -2636,11 +2636,11 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.1897280823443891</v>
+        <v>0</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2651,11 +2651,11 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.36626348840349</v>
+        <v>0</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2666,11 +2666,11 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>1.424195694697974</v>
+        <v>92.98775109907241</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2681,11 +2681,11 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.3474352783346483</v>
+        <v>5.405775384698827</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
